--- a/app/public/business-invoice-template.xlsx
+++ b/app/public/business-invoice-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juliekim/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C4E11D-7A37-EC45-96D7-A85633428468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01934363-8228-0D43-A7B7-55995D99FAF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="사업자" sheetId="6" r:id="rId1"/>
@@ -30,28 +30,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </valueMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -518,28 +496,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -547,15 +503,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="11" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -573,54 +523,82 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="58" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="58" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -638,68 +616,59 @@
 </styleSheet>
 </file>
 
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-</richValueRels>
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>351694</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>9769</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>547078</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>46963</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="그림 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E96C1609-C19A-4176-6B96-48A70A4049EA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2520463" y="175846"/>
+          <a:ext cx="1504461" cy="1248579"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -903,98 +872,96 @@
   <dimension ref="A2:G24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="35"/>
-    <col min="2" max="2" width="17.5" style="43" customWidth="1"/>
-    <col min="3" max="3" width="6.33203125" style="43" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" style="43"/>
-    <col min="5" max="5" width="14.83203125" style="43" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" style="35"/>
-    <col min="7" max="7" width="18.5" style="35" customWidth="1"/>
-    <col min="8" max="16384" width="10.83203125" style="35"/>
+    <col min="1" max="1" width="10.83203125" style="19"/>
+    <col min="2" max="2" width="17.5" style="25" customWidth="1"/>
+    <col min="3" max="3" width="6.33203125" style="25" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" style="25"/>
+    <col min="5" max="5" width="14.83203125" style="25" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" style="19"/>
+    <col min="7" max="7" width="18.5" style="19" customWidth="1"/>
+    <col min="8" max="16384" width="10.83203125" style="19"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:7" ht="95" customHeight="1">
-      <c r="A2" s="51" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
+      <c r="A2" s="41"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
     </row>
     <row r="4" spans="1:7" ht="14" thickBot="1"/>
     <row r="5" spans="1:7" ht="14">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="52"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="22"/>
+      <c r="B5" s="33"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="48"/>
     </row>
     <row r="6" spans="1:7" ht="15">
-      <c r="A6" s="36" t="s">
+      <c r="A6" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="50" t="s">
+      <c r="B6" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="53" t="s">
+      <c r="D6" s="34" t="s">
         <v>16</v>
       </c>
       <c r="E6" s="2"/>
-      <c r="F6" s="23" t="s">
+      <c r="F6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="24"/>
+      <c r="G6" s="12"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="37"/>
-      <c r="B7" s="44"/>
-      <c r="D7" s="25" t="s">
+      <c r="A7" s="21"/>
+      <c r="B7" s="26"/>
+      <c r="D7" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="12"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="26"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="50"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="39"/>
-      <c r="D8" s="27" t="s">
+      <c r="B8" s="45"/>
+      <c r="D8" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="28"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="30"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="53"/>
     </row>
     <row r="9" spans="1:7" ht="15" thickBot="1">
-      <c r="A9" s="40"/>
-      <c r="B9" s="45"/>
-      <c r="D9" s="31" t="s">
+      <c r="A9" s="22"/>
+      <c r="B9" s="27"/>
+      <c r="D9" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="46"/>
-      <c r="F9" s="32" t="s">
+      <c r="E9" s="28"/>
+      <c r="F9" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="33"/>
+      <c r="G9" s="17"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="41"/>
-      <c r="B10" s="41"/>
+      <c r="A10" s="23"/>
+      <c r="B10" s="23"/>
     </row>
     <row r="11" spans="1:7" ht="14" thickBot="1"/>
     <row r="12" spans="1:7" ht="15" thickTop="1">
       <c r="A12" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="42" t="s">
+      <c r="B12" s="24" t="s">
         <v>14</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -1006,10 +973,10 @@
       <c r="E12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="17" t="s">
+      <c r="F12" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="G12" s="11"/>
+      <c r="G12" s="43"/>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="3">
@@ -1019,8 +986,8 @@
       <c r="C13" s="4"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="16"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="36"/>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="3">
@@ -1030,8 +997,8 @@
       <c r="C14" s="4"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="16"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="36"/>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="3">
@@ -1041,8 +1008,8 @@
       <c r="C15" s="4"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="16"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="36"/>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="3">
@@ -1052,8 +1019,8 @@
       <c r="C16" s="4"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="16"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="36"/>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="3">
@@ -1063,8 +1030,8 @@
       <c r="C17" s="4"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="16"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="36"/>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="3">
@@ -1074,8 +1041,8 @@
       <c r="C18" s="4"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="16"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="36"/>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="3">
@@ -1094,10 +1061,10 @@
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="6"/>
-      <c r="D20" s="47"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="16"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="36"/>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="3">
@@ -1105,8 +1072,8 @@
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="6"/>
-      <c r="D21" s="47"/>
-      <c r="E21" s="47"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
       <c r="F21" s="10"/>
       <c r="G21" s="9"/>
     </row>
@@ -1116,46 +1083,47 @@
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="6"/>
-      <c r="D22" s="47"/>
-      <c r="E22" s="48"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="16"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="36"/>
     </row>
     <row r="23" spans="1:7" ht="14" thickBot="1">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="49">
+      <c r="B23" s="38"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="31">
         <f>SUM(E13:E22)</f>
         <v>0</v>
       </c>
-      <c r="F23" s="19"/>
-      <c r="G23" s="14"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="40"/>
     </row>
     <row r="24" spans="1:7" ht="14" thickTop="1"/>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F15:G15"/>
     <mergeCell ref="F16:G16"/>
     <mergeCell ref="F17:G17"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="D5:G5"/>
     <mergeCell ref="E7:G7"/>
     <mergeCell ref="E8:G8"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="F23:G23"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/app/public/business-invoice-template.xlsx
+++ b/app/public/business-invoice-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juliekim/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01934363-8228-0D43-A7B7-55995D99FAF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{54F82D74-D241-9443-B72C-611D0D163023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>No.</t>
   </si>
@@ -81,11 +81,15 @@
     <t>이름</t>
   </si>
   <si>
+    <t>공급자 정보</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사업자명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>사업자번호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>사업자명</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -96,7 +100,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="m\-d"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -111,80 +115,79 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="9"/>
-      <color rgb="FF0563C1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Arial"/>
+      <name val="나눔고딕"/>
       <family val="2"/>
       <charset val="129"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="3"/>
+      <name val="나눔고딕"/>
+      <family val="2"/>
       <charset val="129"/>
     </font>
     <font>
       <sz val="9"/>
+      <name val="나눔고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="나눔고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="나눔고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
       <color theme="1"/>
-      <name val="Malgun Gothic"/>
+      <name val="나눔고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="나눔고딕"/>
       <family val="2"/>
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="23">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -313,45 +316,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
         <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
         <color rgb="FF000000"/>
@@ -364,34 +348,19 @@
     </border>
     <border>
       <left/>
-      <right style="medium">
+      <right/>
+      <top style="thin">
         <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
         <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
       </right>
       <top/>
       <bottom/>
@@ -399,37 +368,11 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -442,166 +385,232 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left/>
+      <right style="thin">
         <color indexed="64"/>
-      </left>
-      <right style="medium">
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="58" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="58" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -620,23 +629,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>351694</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>9769</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>9769</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>107462</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>547078</xdr:colOff>
+      <xdr:colOff>820616</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>46963</xdr:rowOff>
+      <xdr:rowOff>92087</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="그림 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E96C1609-C19A-4176-6B96-48A70A4049EA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76121D53-2FF2-CA99-A454-ABBB4384DA4C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -658,8 +667,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2520463" y="175846"/>
-          <a:ext cx="1504461" cy="1248579"/>
+          <a:off x="2657231" y="107462"/>
+          <a:ext cx="1641231" cy="1362087"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -872,255 +881,298 @@
   <dimension ref="A2:G24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="19"/>
-    <col min="2" max="2" width="17.5" style="25" customWidth="1"/>
-    <col min="3" max="3" width="6.33203125" style="25" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" style="25"/>
-    <col min="5" max="5" width="14.83203125" style="25" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" style="19"/>
-    <col min="7" max="7" width="18.5" style="19" customWidth="1"/>
-    <col min="8" max="16384" width="10.83203125" style="19"/>
+    <col min="1" max="1" width="10.83203125" style="7"/>
+    <col min="2" max="2" width="17.5" style="20" customWidth="1"/>
+    <col min="3" max="3" width="6.33203125" style="20" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" style="20"/>
+    <col min="5" max="5" width="14.83203125" style="20" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" style="7"/>
+    <col min="7" max="7" width="18.5" style="7" customWidth="1"/>
+    <col min="8" max="16384" width="10.83203125" style="7"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:7" ht="95" customHeight="1">
-      <c r="A2" s="41"/>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-    </row>
-    <row r="4" spans="1:7" ht="14" thickBot="1"/>
-    <row r="5" spans="1:7" ht="14">
-      <c r="A5" s="18" t="s">
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="8"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="8"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="33"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="48"/>
-    </row>
-    <row r="6" spans="1:7" ht="15">
-      <c r="A6" s="20" t="s">
+      <c r="B5" s="10"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="48" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="50"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="34" t="s">
+      <c r="C6" s="11"/>
+      <c r="D6" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="12"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="15"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="21"/>
-      <c r="B7" s="26"/>
-      <c r="D7" s="13" t="s">
+      <c r="A7" s="12"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="49"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="50"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="19"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="44" t="s">
+      <c r="C8" s="11"/>
+      <c r="D8" s="38" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="21"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="23"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="45"/>
-      <c r="D8" s="14" t="s">
+      <c r="B9" s="25"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="26"/>
+      <c r="F9" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="26"/>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="16"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+    </row>
+    <row r="11" spans="1:7" ht="14" thickBot="1">
+      <c r="A11" s="27"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+    </row>
+    <row r="12" spans="1:7" ht="14" thickTop="1">
+      <c r="A12" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="52" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="53" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="54"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="1">
+        <v>1</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="31"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="1">
+        <v>2</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="31"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="1">
+        <v>3</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="31"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="1">
+        <v>4</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="31"/>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="1">
         <v>5</v>
       </c>
-      <c r="E8" s="51"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="53"/>
-    </row>
-    <row r="9" spans="1:7" ht="15" thickBot="1">
-      <c r="A9" s="22"/>
-      <c r="B9" s="27"/>
-      <c r="D9" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="28"/>
-      <c r="F9" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="17"/>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="23"/>
-      <c r="B10" s="23"/>
-    </row>
-    <row r="11" spans="1:7" ht="14" thickBot="1"/>
-    <row r="12" spans="1:7" ht="15" thickTop="1">
-      <c r="A12" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="31"/>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="1">
+        <v>6</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="31"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="1">
         <v>7</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="33"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="1">
         <v>8</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="B20" s="2"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="31"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="1">
         <v>9</v>
       </c>
-      <c r="F12" s="42" t="s">
+      <c r="B21" s="2"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="33"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="1">
         <v>10</v>
       </c>
-      <c r="G12" s="43"/>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="3">
-        <v>1</v>
-      </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="36"/>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="3">
-        <v>2</v>
-      </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="36"/>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="3">
-        <v>3</v>
-      </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="36"/>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="3">
-        <v>4</v>
-      </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="36"/>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="3">
-        <v>5</v>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="36"/>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="3">
+      <c r="B22" s="2"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="31"/>
+    </row>
+    <row r="23" spans="1:7" ht="14" thickBot="1">
+      <c r="A23" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="36"/>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="3">
-        <v>7</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="9"/>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="3">
-        <v>8</v>
-      </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="36"/>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="3">
-        <v>9</v>
-      </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="9"/>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="3">
-        <v>10</v>
-      </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="36"/>
-    </row>
-    <row r="23" spans="1:7" ht="14" thickBot="1">
-      <c r="A23" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="38"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="31">
+      <c r="B23" s="45"/>
+      <c r="C23" s="45"/>
+      <c r="D23" s="46"/>
+      <c r="E23" s="47">
         <f>SUM(E13:E22)</f>
         <v>0</v>
       </c>
-      <c r="F23" s="39"/>
-      <c r="G23" s="40"/>
-    </row>
-    <row r="24" spans="1:7" ht="14" thickTop="1"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="35"/>
+    </row>
+    <row r="24" spans="1:7" ht="14" thickTop="1">
+      <c r="A24" s="8"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+    </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="D5:G5"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="F23:G23"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="F13:G13"/>
     <mergeCell ref="F14:G14"/>
     <mergeCell ref="F15:G15"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="E8:G8"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
